--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC06B0CD-76B6-44D8-9F1C-C64864723BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B08702B-2929-486B-AEB6-E27F48EF1C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t>STT</t>
   </si>
@@ -194,6 +194,9 @@
   </si>
   <si>
     <t>865194061565961</t>
+  </si>
+  <si>
+    <t>SIM vật lý</t>
   </si>
 </sst>
 </file>
@@ -599,6 +602,12 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -658,12 +667,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1203,66 +1206,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="46" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="48"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="50"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="50"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="40"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="49" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="52"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="43"/>
-      <c r="B4" s="44"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="51" t="s">
+      <c r="A4" s="45"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="54"/>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
@@ -1317,24 +1320,26 @@
       </c>
     </row>
     <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="54">
+      <c r="A9" s="34">
         <v>1</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="B9" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="35">
         <v>50</v>
       </c>
-      <c r="E9" s="54"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="21"/>
-      <c r="G9" s="54" t="s">
+      <c r="G9" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="54"/>
+      <c r="H9" s="34" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="22"/>
@@ -1497,10 +1502,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="53"/>
+      <c r="B1" s="55"/>
     </row>
     <row r="2" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
@@ -1854,7 +1859,7 @@
       </c>
       <c r="B51" s="33"/>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="30">
         <v>50</v>
       </c>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B08702B-2929-486B-AEB6-E27F48EF1C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5E04DB-508E-44AF-B6CF-A5657A2F1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
   <si>
     <t>STT</t>
   </si>
@@ -197,6 +197,81 @@
   </si>
   <si>
     <t>SIM vật lý</t>
+  </si>
+  <si>
+    <t>865194061564667</t>
+  </si>
+  <si>
+    <t>865194061547340</t>
+  </si>
+  <si>
+    <t>865194061563131</t>
+  </si>
+  <si>
+    <t>865194061565953</t>
+  </si>
+  <si>
+    <t>865194061562133</t>
+  </si>
+  <si>
+    <t>865194061562513</t>
+  </si>
+  <si>
+    <t>865194061564915</t>
+  </si>
+  <si>
+    <t>865194061565300</t>
+  </si>
+  <si>
+    <t>865194061561754</t>
+  </si>
+  <si>
+    <t>865194061568445</t>
+  </si>
+  <si>
+    <t>865194061561879</t>
+  </si>
+  <si>
+    <t>865194061568379</t>
+  </si>
+  <si>
+    <t>865194061565037</t>
+  </si>
+  <si>
+    <t>865194061549973</t>
+  </si>
+  <si>
+    <t>865194061548843</t>
+  </si>
+  <si>
+    <t>865194061563768</t>
+  </si>
+  <si>
+    <t>865194061563230</t>
+  </si>
+  <si>
+    <t>865194061563628</t>
+  </si>
+  <si>
+    <t>865194061565433</t>
+  </si>
+  <si>
+    <t>865194061563040</t>
+  </si>
+  <si>
+    <t>865194061548942</t>
+  </si>
+  <si>
+    <t>865194061564907</t>
+  </si>
+  <si>
+    <t>865194061546979</t>
+  </si>
+  <si>
+    <t>865194061564790</t>
+  </si>
+  <si>
+    <t>865194061564394</t>
   </si>
 </sst>
 </file>
@@ -1719,151 +1794,201 @@
       <c r="A28" s="30">
         <v>26</v>
       </c>
-      <c r="B28" s="33"/>
+      <c r="B28" s="33" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="30">
         <v>27</v>
       </c>
-      <c r="B29" s="33"/>
+      <c r="B29" s="33" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="30">
         <v>28</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="33" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="30">
         <v>29</v>
       </c>
-      <c r="B31" s="33"/>
+      <c r="B31" s="33" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="30">
         <v>30</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="33" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="30">
         <v>31</v>
       </c>
-      <c r="B33" s="33"/>
+      <c r="B33" s="33" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="30">
         <v>32</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="33" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="30">
         <v>33</v>
       </c>
-      <c r="B35" s="33"/>
+      <c r="B35" s="33" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="30">
         <v>34</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="33" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="30">
         <v>35</v>
       </c>
-      <c r="B37" s="33"/>
+      <c r="B37" s="33" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="30">
         <v>36</v>
       </c>
-      <c r="B38" s="33"/>
+      <c r="B38" s="33" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="30">
         <v>37</v>
       </c>
-      <c r="B39" s="33"/>
+      <c r="B39" s="33" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="30">
         <v>38</v>
       </c>
-      <c r="B40" s="33"/>
+      <c r="B40" s="33" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="30">
         <v>39</v>
       </c>
-      <c r="B41" s="33"/>
+      <c r="B41" s="33" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="30">
         <v>40</v>
       </c>
-      <c r="B42" s="33"/>
+      <c r="B42" s="33" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="30">
         <v>41</v>
       </c>
-      <c r="B43" s="33"/>
+      <c r="B43" s="33" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="30">
         <v>42</v>
       </c>
-      <c r="B44" s="33"/>
+      <c r="B44" s="33" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="30">
         <v>43</v>
       </c>
-      <c r="B45" s="33"/>
+      <c r="B45" s="33" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="30">
         <v>44</v>
       </c>
-      <c r="B46" s="33"/>
+      <c r="B46" s="33" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="30">
         <v>45</v>
       </c>
-      <c r="B47" s="33"/>
+      <c r="B47" s="33" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="30">
         <v>46</v>
       </c>
-      <c r="B48" s="33"/>
+      <c r="B48" s="33" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="30">
         <v>47</v>
       </c>
-      <c r="B49" s="33"/>
+      <c r="B49" s="33" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="30">
         <v>48</v>
       </c>
-      <c r="B50" s="33"/>
+      <c r="B50" s="33" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="30">
         <v>49</v>
       </c>
-      <c r="B51" s="33"/>
+      <c r="B51" s="33" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="30">
         <v>50</v>
       </c>
-      <c r="B52" s="33"/>
+      <c r="B52" s="33" t="s">
+        <v>81</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5E04DB-508E-44AF-B6CF-A5657A2F1B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3E5F33-F5A9-4A65-BEDE-D52CE60D67D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="133">
   <si>
     <t>STT</t>
   </si>
@@ -272,6 +272,159 @@
   </si>
   <si>
     <t>865194061564394</t>
+  </si>
+  <si>
+    <t>868694061563818</t>
+  </si>
+  <si>
+    <t>868694061548785</t>
+  </si>
+  <si>
+    <t>868694061564022</t>
+  </si>
+  <si>
+    <t>868694061562752</t>
+  </si>
+  <si>
+    <t>868694061568304</t>
+  </si>
+  <si>
+    <t>868694061549494</t>
+  </si>
+  <si>
+    <t>868694061565110</t>
+  </si>
+  <si>
+    <t>868694061563826</t>
+  </si>
+  <si>
+    <t>868694061546987</t>
+  </si>
+  <si>
+    <t>868694061562364</t>
+  </si>
+  <si>
+    <t>868694061563123</t>
+  </si>
+  <si>
+    <t>868694061565417</t>
+  </si>
+  <si>
+    <t>868694061550195</t>
+  </si>
+  <si>
+    <t>868694061548595</t>
+  </si>
+  <si>
+    <t>868694061566126</t>
+  </si>
+  <si>
+    <t>868694061549429</t>
+  </si>
+  <si>
+    <t>868694061565797</t>
+  </si>
+  <si>
+    <t>868694061568452</t>
+  </si>
+  <si>
+    <t>868694061562992</t>
+  </si>
+  <si>
+    <t>868694061562471</t>
+  </si>
+  <si>
+    <t>868694061561937</t>
+  </si>
+  <si>
+    <t>868694061562646</t>
+  </si>
+  <si>
+    <t>868694061568288</t>
+  </si>
+  <si>
+    <t>868694061562901</t>
+  </si>
+  <si>
+    <t>868694061565961</t>
+  </si>
+  <si>
+    <t>868694061564667</t>
+  </si>
+  <si>
+    <t>868694061547340</t>
+  </si>
+  <si>
+    <t>868694061563131</t>
+  </si>
+  <si>
+    <t>868694061565953</t>
+  </si>
+  <si>
+    <t>868694061562133</t>
+  </si>
+  <si>
+    <t>868694061562513</t>
+  </si>
+  <si>
+    <t>868694061564915</t>
+  </si>
+  <si>
+    <t>868694061565300</t>
+  </si>
+  <si>
+    <t>868694061561754</t>
+  </si>
+  <si>
+    <t>868694061568445</t>
+  </si>
+  <si>
+    <t>868694061561879</t>
+  </si>
+  <si>
+    <t>868694061568379</t>
+  </si>
+  <si>
+    <t>868694061565037</t>
+  </si>
+  <si>
+    <t>868694061549973</t>
+  </si>
+  <si>
+    <t>868694061548843</t>
+  </si>
+  <si>
+    <t>868694061563768</t>
+  </si>
+  <si>
+    <t>868694061563230</t>
+  </si>
+  <si>
+    <t>868694061563628</t>
+  </si>
+  <si>
+    <t>868694061565433</t>
+  </si>
+  <si>
+    <t>868694061563040</t>
+  </si>
+  <si>
+    <t>868694061548942</t>
+  </si>
+  <si>
+    <t>868694061564907</t>
+  </si>
+  <si>
+    <t>868694061546979</t>
+  </si>
+  <si>
+    <t>868694061564790</t>
+  </si>
+  <si>
+    <t>868694061564394</t>
+  </si>
+  <si>
+    <t>IMEI</t>
   </si>
 </sst>
 </file>
@@ -582,7 +735,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -743,6 +896,8 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1569,430 +1724,585 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC994CF-10F2-4E75-9971-34AD9C75ED9B}">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="32" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" style="32" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="55" t="s">
         <v>27</v>
       </c>
       <c r="B1" s="55"/>
-    </row>
-    <row r="2" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="C1" s="55"/>
+    </row>
+    <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="31" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C2" s="57" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>1</v>
       </c>
       <c r="B3" s="33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C3" s="56" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>2</v>
       </c>
       <c r="B4" s="33" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C4" s="56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>3</v>
       </c>
       <c r="B5" s="33" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C5" s="56" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>4</v>
       </c>
       <c r="B6" s="33" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C6" s="56" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>5</v>
       </c>
       <c r="B7" s="33" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C7" s="56" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>6</v>
       </c>
       <c r="B8" s="33" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C8" s="56" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>7</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C9" s="56" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="30">
         <v>8</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C10" s="56" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="30">
         <v>9</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C11" s="56" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
         <v>10</v>
       </c>
       <c r="B12" s="33" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C12" s="56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="30">
         <v>11</v>
       </c>
       <c r="B13" s="33" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C13" s="56" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>12</v>
       </c>
       <c r="B14" s="33" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C14" s="56" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>13</v>
       </c>
       <c r="B15" s="33" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C15" s="56" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>14</v>
       </c>
       <c r="B16" s="33" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C16" s="56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>15</v>
       </c>
       <c r="B17" s="33" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C17" s="56" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>16</v>
       </c>
       <c r="B18" s="33" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C18" s="56" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>17</v>
       </c>
       <c r="B19" s="33" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C19" s="56" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="30">
         <v>18</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C20" s="56" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="30">
         <v>19</v>
       </c>
       <c r="B21" s="33" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C21" s="56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="30">
         <v>20</v>
       </c>
       <c r="B22" s="33" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C22" s="56" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="30">
         <v>21</v>
       </c>
       <c r="B23" s="33" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C23" s="56" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="30">
         <v>22</v>
       </c>
       <c r="B24" s="33" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C24" s="56" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>23</v>
       </c>
       <c r="B25" s="33" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C25" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="30">
         <v>24</v>
       </c>
       <c r="B26" s="33" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C26" s="56" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="30">
         <v>25</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C27" s="56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="30">
         <v>26</v>
       </c>
       <c r="B28" s="33" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C28" s="56" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>27</v>
       </c>
       <c r="B29" s="33" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C29" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>28</v>
       </c>
       <c r="B30" s="33" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C30" s="56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="30">
         <v>29</v>
       </c>
       <c r="B31" s="33" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C31" s="56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="30">
         <v>30</v>
       </c>
       <c r="B32" s="33" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C32" s="56" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="30">
         <v>31</v>
       </c>
       <c r="B33" s="33" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C33" s="56" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="30">
         <v>32</v>
       </c>
       <c r="B34" s="33" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C34" s="56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="30">
         <v>33</v>
       </c>
       <c r="B35" s="33" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C35" s="56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="30">
         <v>34</v>
       </c>
       <c r="B36" s="33" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C36" s="56" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="30">
         <v>35</v>
       </c>
       <c r="B37" s="33" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C37" s="56" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="30">
         <v>36</v>
       </c>
       <c r="B38" s="33" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C38" s="56" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="30">
         <v>37</v>
       </c>
       <c r="B39" s="33" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C39" s="56" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="30">
         <v>38</v>
       </c>
       <c r="B40" s="33" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C40" s="56" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="30">
         <v>39</v>
       </c>
       <c r="B41" s="33" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C41" s="56" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>40</v>
       </c>
       <c r="B42" s="33" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C42" s="56" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="30">
         <v>41</v>
       </c>
       <c r="B43" s="33" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C43" s="56" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="30">
         <v>42</v>
       </c>
       <c r="B44" s="33" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C44" s="56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="30">
         <v>43</v>
       </c>
       <c r="B45" s="33" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C45" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="30">
         <v>44</v>
       </c>
       <c r="B46" s="33" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C46" s="56" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="30">
         <v>45</v>
       </c>
       <c r="B47" s="33" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C47" s="56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="30">
         <v>46</v>
       </c>
       <c r="B48" s="33" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C48" s="56" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="30">
         <v>47</v>
       </c>
       <c r="B49" s="33" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C49" s="56" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="30">
         <v>48</v>
       </c>
       <c r="B50" s="33" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C50" s="56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="30">
         <v>49</v>
       </c>
       <c r="B51" s="33" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="C51" s="56" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="30">
         <v>50</v>
       </c>
       <c r="B52" s="33" t="s">
         <v>81</v>
       </c>
+      <c r="C52" s="56" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3">
     <cfRule type="duplicateValues" dxfId="10" priority="11"/>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 08/NKSX_TG102LE(8686)-SL50_260826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 08\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3E5F33-F5A9-4A65-BEDE-D52CE60D67D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{416F7FC5-3C66-4D79-BD6F-C7A84D60F7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,7 +424,7 @@
     <t>868694061564394</t>
   </si>
   <si>
-    <t>IMEI</t>
+    <t>IMEI_TG102LE(8686)</t>
   </si>
 </sst>
 </file>
@@ -836,6 +836,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -896,8 +898,6 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1436,66 +1436,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="48" t="s">
+      <c r="B1" s="42"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="50"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="52"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="51" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="52"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="54"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="51" t="s">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="54"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="53" t="s">
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="54"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="56"/>
     </row>
     <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="40"/>
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
@@ -1728,26 +1728,26 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="32" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" style="32" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" style="32" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
@@ -1757,7 +1757,7 @@
       <c r="B3" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="36" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       <c r="B4" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="36" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       <c r="B5" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="36" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       <c r="B6" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="36" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       <c r="B7" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="36" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       <c r="B8" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="36" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       <c r="B9" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="36" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1834,7 +1834,7 @@
       <c r="B10" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="36" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       <c r="B11" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="36" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       <c r="B12" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="36" t="s">
         <v>91</v>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       <c r="B13" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="36" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       <c r="B14" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="36" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1889,7 +1889,7 @@
       <c r="B15" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="36" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       <c r="B16" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="36" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       <c r="B17" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="36" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       <c r="B18" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="36" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       <c r="B19" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="36" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       <c r="B20" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="36" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       <c r="B21" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="56" t="s">
+      <c r="C21" s="36" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       <c r="B22" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="36" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       <c r="B23" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="56" t="s">
+      <c r="C23" s="36" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       <c r="B24" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="36" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       <c r="B25" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="36" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       <c r="B26" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="56" t="s">
+      <c r="C26" s="36" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       <c r="B27" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="36" t="s">
         <v>106</v>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       <c r="B28" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="36" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       <c r="B29" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="56" t="s">
+      <c r="C29" s="36" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       <c r="B30" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="36" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       <c r="B31" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="56" t="s">
+      <c r="C31" s="36" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       <c r="B32" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="36" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       <c r="B33" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="56" t="s">
+      <c r="C33" s="36" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       <c r="B34" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="56" t="s">
+      <c r="C34" s="36" t="s">
         <v>113</v>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       <c r="B35" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="56" t="s">
+      <c r="C35" s="36" t="s">
         <v>114</v>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       <c r="B36" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="C36" s="36" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       <c r="B37" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="36" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
       <c r="B38" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="36" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       <c r="B39" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="56" t="s">
+      <c r="C39" s="36" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       <c r="B40" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="56" t="s">
+      <c r="C40" s="36" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       <c r="B41" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="56" t="s">
+      <c r="C41" s="36" t="s">
         <v>120</v>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       <c r="B42" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="C42" s="56" t="s">
+      <c r="C42" s="36" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       <c r="B43" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="C43" s="56" t="s">
+      <c r="C43" s="36" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       <c r="B44" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="56" t="s">
+      <c r="C44" s="36" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       <c r="B45" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="36" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       <c r="B46" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="36" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       <c r="B47" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="56" t="s">
+      <c r="C47" s="36" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       <c r="B48" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="56" t="s">
+      <c r="C48" s="36" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       <c r="B49" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="56" t="s">
+      <c r="C49" s="36" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       <c r="B50" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="56" t="s">
+      <c r="C50" s="36" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       <c r="B51" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="C51" s="56" t="s">
+      <c r="C51" s="36" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       <c r="B52" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C52" s="36" t="s">
         <v>131</v>
       </c>
     </row>
